--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AccountAmount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AccountAmount001.xlsx
@@ -465,8 +465,8 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
-      <formula1>"6405,6407"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576">
+      <formula1>"6605,6407"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
